--- a/Result/profitability/3591.xlsx
+++ b/Result/profitability/3591.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12</v>
+        <v>0.09749999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>23.03875</v>
+        <v>22.5625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.66</v>
       </c>
       <c r="M3" t="n">
-        <v>0.175</v>
+        <v>0.14625</v>
       </c>
       <c r="N3" t="n">
-        <v>23.18875</v>
+        <v>22.7425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.84</v>
       </c>
       <c r="M4" t="n">
-        <v>0.37125</v>
+        <v>0.365</v>
       </c>
       <c r="N4" t="n">
-        <v>23.72125</v>
+        <v>23.40625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.93</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4762500000000001</v>
+        <v>0.49625</v>
       </c>
       <c r="N5" t="n">
-        <v>24.41125</v>
+        <v>24.25375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>0.67125</v>
+        <v>0.69875</v>
       </c>
       <c r="N6" t="n">
-        <v>25.95625</v>
+        <v>26.2425</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9225000000000001</v>
+        <v>0.9437500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>27.755</v>
+        <v>27.64875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.3</v>
@@ -1391,10 +1391,10 @@
         <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1375</v>
+        <v>1.1275</v>
       </c>
       <c r="N8" t="n">
-        <v>29.6225</v>
+        <v>29.42</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>690</v>
+      </c>
+      <c r="D74" t="n">
+        <v>548</v>
+      </c>
+      <c r="E74" t="n">
+        <v>142</v>
+      </c>
+      <c r="F74" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="G74" t="n">
+        <v>24</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J74" t="n">
+        <v>22</v>
+      </c>
+      <c r="K74" t="n">
+        <v>6</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.03875</v>
+      </c>
+      <c r="N74" t="n">
+        <v>22.0475</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-0.07999999999999999</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>-1.620000000000001</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>-0.07280898876404496</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>-1.260000000000002</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>-0.05756052992233907</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
